--- a/426-config---paramètre-pin-all/ig/StructureDefinition-tddui-patient-ins.xlsx
+++ b/426-config---paramètre-pin-all/ig/StructureDefinition-tddui-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7663" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7663" uniqueCount="871">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T15:49:47+00:00</t>
+    <t>2026-01-30T16:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -449,7 +449,7 @@
     <t>Patient.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
   </si>
   <si>
     <t>Patient.meta.security</t>
@@ -503,7 +503,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -527,7 +527,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -570,7 +570,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -649,7 +649,7 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
 </t>
   </si>
   <si>
@@ -669,7 +669,7 @@
     <t>identityReliability</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability}
 </t>
   </si>
   <si>
@@ -685,7 +685,7 @@
     <t>deathPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
 </t>
   </si>
   <si>
@@ -701,7 +701,7 @@
     <t>birthdateUpdateIndicator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
 </t>
   </si>
   <si>
@@ -714,7 +714,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
+    <t xml:space="preserve">Extension {patient-birthPlace}
 </t>
   </si>
   <si>
@@ -763,7 +763,7 @@
     <t>Patient.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
@@ -803,7 +803,7 @@
     <t>inseeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code}
 </t>
   </si>
   <si>
@@ -1212,7 +1212,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-patient-identifier-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-patient-identifier-vs</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1353,7 +1353,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NSS.system</t>
@@ -1369,6 +1369,10 @@
   </si>
   <si>
     <t>Patient.identifier:NSS.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
   </si>
   <si>
     <t>Patient.identifier:INS-C</t>
@@ -1781,6 +1785,9 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
     <t>Patient.identifier:InitialNumberMDPH.system</t>
   </si>
   <si>
@@ -1827,7 +1834,7 @@
     <t>Patient.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-human-name|2.2.0-ballot}
+    <t xml:space="preserve">HumanName {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-human-name}
 </t>
   </si>
   <si>
@@ -2080,7 +2087,7 @@
     <t>birth-list-given-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name}
 </t>
   </si>
   <si>
@@ -2129,7 +2136,7 @@
     <t>Patient.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -2170,7 +2177,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender-INS|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender-INS</t>
   </si>
   <si>
     <t>sexe</t>
@@ -2262,7 +2269,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -2365,7 +2372,7 @@
     <t>contactIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
 </t>
   </si>
   <si>
@@ -2381,7 +2388,7 @@
     <t>comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
 </t>
   </si>
   <si>
@@ -2423,7 +2430,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -2445,7 +2452,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelationType</t>
@@ -2457,13 +2464,13 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.1.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
 </t>
   </si>
   <si>
@@ -2653,7 +2660,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.1.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
 </t>
   </si>
   <si>
@@ -2677,7 +2684,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2728,7 +2735,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -3086,7 +3093,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="137.58984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="124.00390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3101,7 +3108,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="64.48046875" customWidth="true" bestFit="true"/>
@@ -10101,7 +10108,7 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>412</v>
@@ -10195,13 +10202,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
@@ -10226,7 +10233,7 @@
         <v>357</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>359</v>
@@ -10317,7 +10324,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>367</v>
@@ -10435,7 +10442,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>368</v>
@@ -10555,7 +10562,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>369</v>
@@ -10603,7 +10610,7 @@
         <v>82</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>82</v>
@@ -10677,7 +10684,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>378</v>
@@ -10709,7 +10716,7 @@
         <v>380</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>382</v>
@@ -10725,7 +10732,7 @@
         <v>82</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>82</v>
@@ -10799,7 +10806,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>387</v>
@@ -10847,7 +10854,7 @@
         <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>392</v>
@@ -10921,7 +10928,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>396</v>
@@ -11041,7 +11048,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>404</v>
@@ -11159,7 +11166,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>410</v>
@@ -11185,7 +11192,7 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>412</v>
@@ -11279,13 +11286,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -11310,7 +11317,7 @@
         <v>357</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
         <v>359</v>
@@ -11401,7 +11408,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>367</v>
@@ -11519,7 +11526,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>368</v>
@@ -11639,7 +11646,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>369</v>
@@ -11687,7 +11694,7 @@
         <v>82</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>82</v>
@@ -11761,7 +11768,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>378</v>
@@ -11809,7 +11816,7 @@
         <v>82</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>82</v>
@@ -11883,7 +11890,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>387</v>
@@ -11931,7 +11938,7 @@
         <v>82</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>392</v>
@@ -12005,7 +12012,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>396</v>
@@ -12125,7 +12132,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>404</v>
@@ -12243,7 +12250,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>410</v>
@@ -12269,7 +12276,7 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>412</v>
@@ -12363,13 +12370,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -12394,7 +12401,7 @@
         <v>357</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>359</v>
@@ -12465,7 +12472,7 @@
         <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>363</v>
@@ -12485,7 +12492,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>367</v>
@@ -12603,7 +12610,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>368</v>
@@ -12723,7 +12730,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>369</v>
@@ -12771,7 +12778,7 @@
         <v>82</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>82</v>
@@ -12845,7 +12852,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>378</v>
@@ -12893,7 +12900,7 @@
         <v>82</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>82</v>
@@ -12967,7 +12974,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>387</v>
@@ -13015,7 +13022,7 @@
         <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>392</v>
@@ -13089,7 +13096,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>396</v>
@@ -13209,7 +13216,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>404</v>
@@ -13327,7 +13334,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>410</v>
@@ -13353,7 +13360,7 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>412</v>
@@ -13447,13 +13454,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>82</v>
@@ -13478,7 +13485,7 @@
         <v>357</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>359</v>
@@ -13569,7 +13576,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>367</v>
@@ -13687,7 +13694,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>368</v>
@@ -13807,7 +13814,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>369</v>
@@ -13855,7 +13862,7 @@
         <v>82</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>82</v>
@@ -13929,7 +13936,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>378</v>
@@ -13977,7 +13984,7 @@
         <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>82</v>
@@ -14051,7 +14058,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>387</v>
@@ -14173,7 +14180,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>396</v>
@@ -14293,7 +14300,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>404</v>
@@ -14411,7 +14418,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>410</v>
@@ -14437,7 +14444,7 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>412</v>
@@ -14531,13 +14538,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>82</v>
@@ -14562,7 +14569,7 @@
         <v>357</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M96" t="s" s="2">
         <v>359</v>
@@ -14633,7 +14640,7 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>363</v>
@@ -14653,7 +14660,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>367</v>
@@ -14771,7 +14778,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>368</v>
@@ -14891,7 +14898,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>369</v>
@@ -15013,7 +15020,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>378</v>
@@ -15061,7 +15068,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -15135,7 +15142,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>387</v>
@@ -15164,7 +15171,7 @@
         <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>389</v>
@@ -15257,7 +15264,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>396</v>
@@ -15377,7 +15384,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>404</v>
@@ -15495,7 +15502,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>410</v>
@@ -15521,7 +15528,7 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>412</v>
@@ -15615,13 +15622,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>82</v>
@@ -15646,7 +15653,7 @@
         <v>357</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>359</v>
@@ -15737,7 +15744,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>367</v>
@@ -15855,7 +15862,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>368</v>
@@ -15975,7 +15982,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>369</v>
@@ -16097,7 +16104,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>378</v>
@@ -16145,7 +16152,7 @@
         <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>82</v>
@@ -16219,7 +16226,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>387</v>
@@ -16248,7 +16255,7 @@
         <v>133</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>389</v>
@@ -16267,7 +16274,7 @@
         <v>82</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>392</v>
@@ -16341,7 +16348,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>396</v>
@@ -16461,7 +16468,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>404</v>
@@ -16579,7 +16586,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>410</v>
@@ -16605,7 +16612,7 @@
         <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>412</v>
@@ -16699,13 +16706,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>82</v>
@@ -16730,7 +16737,7 @@
         <v>357</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>359</v>
@@ -16821,7 +16828,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>367</v>
@@ -16939,7 +16946,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>368</v>
@@ -17059,7 +17066,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>369</v>
@@ -17181,7 +17188,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>378</v>
@@ -17229,7 +17236,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -17303,7 +17310,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>387</v>
@@ -17332,7 +17339,7 @@
         <v>133</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>389</v>
@@ -17351,7 +17358,7 @@
         <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>392</v>
@@ -17425,7 +17432,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>396</v>
@@ -17545,7 +17552,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>404</v>
@@ -17663,7 +17670,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>410</v>
@@ -17689,7 +17696,7 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>412</v>
@@ -17783,13 +17790,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -17814,7 +17821,7 @@
         <v>357</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M123" t="s" s="2">
         <v>359</v>
@@ -17885,7 +17892,7 @@
         <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>363</v>
@@ -17905,7 +17912,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>367</v>
@@ -18023,7 +18030,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>368</v>
@@ -18143,7 +18150,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>369</v>
@@ -18191,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -18265,7 +18272,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>378</v>
@@ -18313,7 +18320,7 @@
         <v>82</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>82</v>
@@ -18387,7 +18394,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>387</v>
@@ -18416,7 +18423,7 @@
         <v>133</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>389</v>
@@ -18435,7 +18442,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>392</v>
@@ -18509,7 +18516,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>396</v>
@@ -18629,7 +18636,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>404</v>
@@ -18747,7 +18754,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>410</v>
@@ -18773,7 +18780,7 @@
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L131" t="s" s="2">
         <v>412</v>
@@ -18867,13 +18874,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>82</v>
@@ -18898,7 +18905,7 @@
         <v>357</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M132" t="s" s="2">
         <v>359</v>
@@ -18969,7 +18976,7 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>363</v>
@@ -18989,7 +18996,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>367</v>
@@ -19107,7 +19114,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>368</v>
@@ -19227,7 +19234,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>369</v>
@@ -19275,7 +19282,7 @@
         <v>82</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>82</v>
@@ -19349,7 +19356,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>378</v>
@@ -19397,7 +19404,7 @@
         <v>82</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>82</v>
@@ -19418,7 +19425,7 @@
         <v>428</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>429</v>
+        <v>556</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -19471,7 +19478,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>387</v>
@@ -19593,7 +19600,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>396</v>
@@ -19713,7 +19720,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>404</v>
@@ -19831,7 +19838,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>410</v>
@@ -19951,10 +19958,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19977,70 +19984,70 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q141" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="R141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF141" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="P141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q141" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="R141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20058,13 +20065,13 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -20075,10 +20082,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20101,19 +20108,19 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -20150,7 +20157,7 @@
         <v>82</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
@@ -20160,7 +20167,7 @@
         <v>118</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20178,16 +20185,16 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>82</v>
@@ -20195,13 +20202,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>82</v>
@@ -20223,19 +20230,19 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -20284,7 +20291,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20302,16 +20309,16 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>82</v>
@@ -20319,10 +20326,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20437,10 +20444,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20557,10 +20564,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20586,16 +20593,16 @@
         <v>172</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20605,7 +20612,7 @@
         <v>82</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>82</v>
@@ -20623,10 +20630,10 @@
         <v>263</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20644,7 +20651,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20671,7 +20678,7 @@
         <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AP146" t="s" s="2">
         <v>82</v>
@@ -20679,10 +20686,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20708,13 +20715,13 @@
         <v>105</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>284</v>
@@ -20766,7 +20773,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20793,7 +20800,7 @@
         <v>82</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>82</v>
@@ -20801,14 +20808,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -20830,13 +20837,13 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20886,7 +20893,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20901,10 +20908,10 @@
         <v>103</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>82</v>
@@ -20913,7 +20920,7 @@
         <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AP148" t="s" s="2">
         <v>82</v>
@@ -20921,14 +20928,14 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20950,13 +20957,13 @@
         <v>105</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -21006,7 +21013,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21021,10 +21028,10 @@
         <v>103</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
@@ -21033,7 +21040,7 @@
         <v>82</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>82</v>
@@ -21041,10 +21048,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21070,10 +21077,10 @@
         <v>105</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -21124,7 +21131,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21142,7 +21149,7 @@
         <v>82</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
@@ -21151,7 +21158,7 @@
         <v>82</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>82</v>
@@ -21159,10 +21166,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21188,10 +21195,10 @@
         <v>105</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -21242,7 +21249,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21260,7 +21267,7 @@
         <v>82</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>82</v>
@@ -21269,7 +21276,7 @@
         <v>82</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>82</v>
@@ -21277,10 +21284,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21306,14 +21313,14 @@
         <v>343</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -21362,7 +21369,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21389,7 +21396,7 @@
         <v>82</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>82</v>
@@ -21397,13 +21404,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>82</v>
@@ -21425,19 +21432,19 @@
         <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -21486,7 +21493,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21504,16 +21511,16 @@
         <v>82</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AP153" t="s" s="2">
         <v>82</v>
@@ -21521,10 +21528,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21639,10 +21646,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21757,13 +21764,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>82</v>
@@ -21785,13 +21792,13 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21857,7 +21864,7 @@
         <v>120</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>82</v>
@@ -21877,10 +21884,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21906,16 +21913,16 @@
         <v>172</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21943,10 +21950,10 @@
         <v>263</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>82</v>
@@ -21964,7 +21971,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21991,7 +21998,7 @@
         <v>82</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AP157" t="s" s="2">
         <v>82</v>
@@ -21999,10 +22006,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22028,13 +22035,13 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O158" t="s" s="2">
         <v>284</v>
@@ -22086,7 +22093,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -22113,7 +22120,7 @@
         <v>82</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AP158" t="s" s="2">
         <v>82</v>
@@ -22121,14 +22128,14 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -22150,13 +22157,13 @@
         <v>105</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22206,7 +22213,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22221,10 +22228,10 @@
         <v>103</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>82</v>
@@ -22233,7 +22240,7 @@
         <v>82</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>82</v>
@@ -22241,14 +22248,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -22270,13 +22277,13 @@
         <v>105</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -22326,7 +22333,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22341,10 +22348,10 @@
         <v>103</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>82</v>
@@ -22353,7 +22360,7 @@
         <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AP160" t="s" s="2">
         <v>82</v>
@@ -22361,10 +22368,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22390,10 +22397,10 @@
         <v>105</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -22444,7 +22451,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -22459,10 +22466,10 @@
         <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
@@ -22471,7 +22478,7 @@
         <v>82</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AP161" t="s" s="2">
         <v>82</v>
@@ -22479,10 +22486,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22508,10 +22515,10 @@
         <v>105</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22562,7 +22569,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22580,7 +22587,7 @@
         <v>82</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>82</v>
@@ -22589,7 +22596,7 @@
         <v>82</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>82</v>
@@ -22597,10 +22604,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22626,14 +22633,14 @@
         <v>343</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22682,7 +22689,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22709,7 +22716,7 @@
         <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>82</v>
@@ -22717,10 +22724,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22743,19 +22750,19 @@
         <v>82</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22804,7 +22811,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22816,13 +22823,13 @@
         <v>206</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>82</v>
@@ -22831,7 +22838,7 @@
         <v>82</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>82</v>
@@ -22839,10 +22846,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22868,16 +22875,16 @@
         <v>172</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22906,7 +22913,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22924,7 +22931,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22939,19 +22946,19 @@
         <v>103</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>82</v>
@@ -22959,10 +22966,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22985,19 +22992,19 @@
         <v>92</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -23046,7 +23053,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23061,30 +23068,30 @@
         <v>103</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23107,19 +23114,19 @@
         <v>92</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -23168,7 +23175,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -23186,7 +23193,7 @@
         <v>82</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>109</v>
@@ -23195,7 +23202,7 @@
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>82</v>
@@ -23203,10 +23210,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23241,7 +23248,7 @@
         <v>242</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -23290,7 +23297,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23325,10 +23332,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23354,14 +23361,14 @@
         <v>379</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -23390,7 +23397,7 @@
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -23408,7 +23415,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23426,16 +23433,16 @@
         <v>82</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AP169" t="s" s="2">
         <v>82</v>
@@ -23443,10 +23450,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23469,19 +23476,19 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -23530,7 +23537,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -23548,7 +23555,7 @@
         <v>82</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>109</v>
@@ -23557,7 +23564,7 @@
         <v>82</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AP170" t="s" s="2">
         <v>82</v>
@@ -23565,10 +23572,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23591,19 +23598,19 @@
         <v>82</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -23652,7 +23659,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23670,7 +23677,7 @@
         <v>82</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>109</v>
@@ -23679,7 +23686,7 @@
         <v>82</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>82</v>
@@ -23687,10 +23694,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23713,19 +23720,19 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23774,7 +23781,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23786,13 +23793,13 @@
         <v>82</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>109</v>
@@ -23809,10 +23816,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23927,10 +23934,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24043,13 +24050,13 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>82</v>
@@ -24071,13 +24078,13 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -24163,13 +24170,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>82</v>
@@ -24191,13 +24198,13 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24283,14 +24290,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -24312,10 +24319,10 @@
         <v>112</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>115</v>
@@ -24370,7 +24377,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24405,10 +24412,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24434,14 +24441,14 @@
         <v>379</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -24469,16 +24476,16 @@
         <v>154</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
@@ -24488,7 +24495,7 @@
         <v>118</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24506,7 +24513,7 @@
         <v>82</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>109</v>
@@ -24515,7 +24522,7 @@
         <v>82</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>82</v>
@@ -24523,13 +24530,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>82</v>
@@ -24554,14 +24561,14 @@
         <v>379</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24590,7 +24597,7 @@
       </c>
       <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -24608,7 +24615,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24626,7 +24633,7 @@
         <v>82</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>109</v>
@@ -24635,7 +24642,7 @@
         <v>82</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AP179" t="s" s="2">
         <v>82</v>
@@ -24643,13 +24650,13 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>82</v>
@@ -24674,14 +24681,14 @@
         <v>379</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24710,7 +24717,7 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -24728,7 +24735,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24746,7 +24753,7 @@
         <v>82</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>109</v>
@@ -24755,7 +24762,7 @@
         <v>82</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>82</v>
@@ -24763,10 +24770,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24789,19 +24796,19 @@
         <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24850,7 +24857,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24868,7 +24875,7 @@
         <v>82</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>82</v>
@@ -24877,7 +24884,7 @@
         <v>82</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AP181" t="s" s="2">
         <v>82</v>
@@ -24885,10 +24892,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24911,19 +24918,19 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24972,7 +24979,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24984,13 +24991,13 @@
         <v>206</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>82</v>
@@ -24999,7 +25006,7 @@
         <v>82</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AP182" t="s" s="2">
         <v>82</v>
@@ -25007,10 +25014,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25033,17 +25040,17 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -25092,7 +25099,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -25110,7 +25117,7 @@
         <v>82</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>109</v>
@@ -25119,7 +25126,7 @@
         <v>82</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AP183" t="s" s="2">
         <v>82</v>
@@ -25127,10 +25134,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25156,14 +25163,14 @@
         <v>172</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -25191,10 +25198,10 @@
         <v>263</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -25212,7 +25219,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -25230,7 +25237,7 @@
         <v>82</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>109</v>
@@ -25239,7 +25246,7 @@
         <v>82</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>82</v>
@@ -25247,10 +25254,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25273,17 +25280,17 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -25332,7 +25339,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -25341,7 +25348,7 @@
         <v>91</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>103</v>
@@ -25350,7 +25357,7 @@
         <v>82</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>109</v>
@@ -25359,7 +25366,7 @@
         <v>82</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>82</v>
@@ -25367,10 +25374,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25396,10 +25403,10 @@
         <v>343</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25450,7 +25457,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25468,7 +25475,7 @@
         <v>82</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>109</v>
@@ -25485,10 +25492,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25511,19 +25518,19 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -25572,7 +25579,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25590,10 +25597,10 @@
         <v>82</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -25607,10 +25614,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25725,10 +25732,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25845,14 +25852,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -25874,10 +25881,10 @@
         <v>112</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>115</v>
@@ -25932,7 +25939,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -25967,10 +25974,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25996,16 +26003,16 @@
         <v>379</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -26054,7 +26061,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>91</v>
@@ -26072,16 +26079,16 @@
         <v>82</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>82</v>
@@ -26089,10 +26096,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26115,19 +26122,19 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -26176,7 +26183,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -26194,16 +26201,16 @@
         <v>82</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>82</v>
@@ -26211,14 +26218,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -26237,16 +26244,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26296,7 +26303,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -26314,7 +26321,7 @@
         <v>82</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>109</v>
@@ -26323,7 +26330,7 @@
         <v>82</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AP193" t="s" s="2">
         <v>82</v>
@@ -26331,10 +26338,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26357,19 +26364,19 @@
         <v>92</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -26418,7 +26425,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26436,10 +26443,10 @@
         <v>82</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>82</v>
@@ -26453,10 +26460,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26479,19 +26486,19 @@
         <v>92</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>82</v>
@@ -26540,7 +26547,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26558,7 +26565,7 @@
         <v>82</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>109</v>
@@ -26575,10 +26582,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26693,10 +26700,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26813,14 +26820,14 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
@@ -26842,10 +26849,10 @@
         <v>112</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N198" t="s" s="2">
         <v>115</v>
@@ -26900,7 +26907,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -26935,10 +26942,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26961,16 +26968,16 @@
         <v>92</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -27020,7 +27027,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>91</v>
@@ -27047,7 +27054,7 @@
         <v>82</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>82</v>
@@ -27055,10 +27062,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27084,10 +27091,10 @@
         <v>172</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -27117,28 +27124,28 @@
         <v>263</v>
       </c>
       <c r="Y200" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="Z200" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="AA200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF200" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="Z200" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>91</v>
@@ -27156,7 +27163,7 @@
         <v>82</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>109</v>
